--- a/upload/despesa_pessoal_mensal.xlsx
+++ b/upload/despesa_pessoal_mensal.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17295" windowHeight="6390"/>
   </bookViews>
   <sheets>
     <sheet name="despesa_pessoal_mensal" sheetId="1" r:id="rId1"/>
@@ -21,31 +21,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="52">
   <si>
-    <t>DESPESA BRUTA COM PESSOAL (I)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> -   </t>
-  </si>
-  <si>
-    <t>Pessoal Ativo</t>
-  </si>
-  <si>
-    <t>Vencimentos, Vantagens e Outras Despesas Variáveis</t>
-  </si>
-  <si>
-    <t>Obrigações Patronais</t>
-  </si>
-  <si>
-    <t>Pessoal Inativo e Pensionistas</t>
-  </si>
-  <si>
-    <t>Aposentadorias, Reserva e Reformas</t>
-  </si>
-  <si>
-    <t>Pensões</t>
-  </si>
-  <si>
-    <t>Outras Despesas de Pessoal Decorrentes de Contratos de Terceirização ou de Contratação de Forma Indireta (§ 1º do art. 18 da LRF)</t>
   </si>
   <si>
     <t>mai-23</t>
@@ -175,6 +151,30 @@
   </si>
   <si>
     <t>despesa_liquida_pessoal</t>
+  </si>
+  <si>
+    <t>despesa_bruta_com_pessoal_I</t>
+  </si>
+  <si>
+    <t>pessoal_ativo</t>
+  </si>
+  <si>
+    <t>vencimentos_vantagens_e_outras</t>
+  </si>
+  <si>
+    <t>outras_despesas_terceirizacoes</t>
+  </si>
+  <si>
+    <t>pensoes</t>
+  </si>
+  <si>
+    <t>aposentadorias_reservas_e_reformas</t>
+  </si>
+  <si>
+    <t>pessoal_inativo_e_pensionistas</t>
+  </si>
+  <si>
+    <t>obrigacoes_patronais</t>
   </si>
 </sst>
 </file>
@@ -1078,66 +1078,66 @@
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="5" t="s">
+      <c r="N1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="R1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="4" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B2" s="6">
         <v>4102729301.0700002</v>
@@ -1161,7 +1161,7 @@
         <v>359080112.11000001</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="6">
         <v>-41123718.399999999</v>
@@ -1182,13 +1182,13 @@
         <v>689649252.76999998</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" s="1">
         <v>3379113684.1900001</v>
@@ -1196,7 +1196,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="4" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B3" s="6">
         <v>4134753101.8000002</v>
@@ -1220,7 +1220,7 @@
         <v>346622237.50999999</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="6">
         <v>42784527.460000001</v>
@@ -1241,13 +1241,13 @@
         <v>651819182.15999997</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" s="1">
         <v>3449471345.6700001</v>
@@ -1255,7 +1255,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="4" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B4" s="6">
         <v>4365127462.1800003</v>
@@ -1279,7 +1279,7 @@
         <v>356845469.47000003</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="6">
         <v>30294631.68</v>
@@ -1300,13 +1300,13 @@
         <v>645803961.14999998</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" s="1">
         <v>3681001632.2600002</v>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="4" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B5" s="6">
         <v>4749291854.6000004</v>
@@ -1338,7 +1338,7 @@
         <v>361779945.36000001</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="6">
         <v>271250607.41000003</v>
@@ -1359,13 +1359,13 @@
         <v>691826032.78999996</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" s="1">
         <v>4024677340.0999999</v>
@@ -1373,7 +1373,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="4" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B6" s="6">
         <v>4737908259.96</v>
@@ -1397,7 +1397,7 @@
         <v>355288273.16000003</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="6">
         <v>-350407564.43000001</v>
@@ -1418,13 +1418,13 @@
         <v>558082388.80999994</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" s="1">
         <v>4052039784.8400002</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B7" s="6">
         <v>4704099845.4399996</v>
@@ -1456,7 +1456,7 @@
         <v>354905648.06</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="6">
         <v>3133361.14</v>
@@ -1477,13 +1477,13 @@
         <v>506126882.38999999</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" s="1">
         <v>4131174083.4699998</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B8" s="6">
         <v>5529623295.6599998</v>
@@ -1515,7 +1515,7 @@
         <v>356370244.41000003</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="6">
         <v>239765490.83000001</v>
@@ -1536,13 +1536,13 @@
         <v>637916237.05999994</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" s="1">
         <v>4718114849.46</v>
@@ -1550,7 +1550,7 @@
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B9" s="6">
         <v>8243411483.1899996</v>
@@ -1574,7 +1574,7 @@
         <v>690816855.85000002</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" s="6">
         <v>107508712.45999999</v>
@@ -1595,13 +1595,13 @@
         <v>1588903808.6900001</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" s="1">
         <v>6170924652.75</v>
@@ -1609,7 +1609,7 @@
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B10" s="6">
         <v>4360614719.8500004</v>
@@ -1633,7 +1633,7 @@
         <v>366319684.19999999</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="6">
         <v>5155541.0599999996</v>
@@ -1654,13 +1654,13 @@
         <v>656139970.38999999</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" s="1">
         <v>3677570567.4299998</v>
@@ -1668,7 +1668,7 @@
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="4" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B11" s="6">
         <v>4542452747.0600004</v>
@@ -1692,7 +1692,7 @@
         <v>356371210.60000002</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="6">
         <v>-3795020.04</v>
@@ -1713,13 +1713,13 @@
         <v>699661569.85000002</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" s="1">
         <v>3764223386.3600001</v>
@@ -1727,7 +1727,7 @@
     </row>
     <row r="12" spans="1:19">
       <c r="A12" s="4" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B12" s="6">
         <v>4382405735.6599998</v>
@@ -1751,7 +1751,7 @@
         <v>364716297.14999998</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="6">
         <v>9201203.1600000001</v>
@@ -1772,13 +1772,13 @@
         <v>720344221.15999997</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" s="1">
         <v>3630452380.9000001</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="4" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B13" s="6">
         <v>4408807782.6400003</v>
@@ -1810,7 +1810,7 @@
         <v>365471175.83999997</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="6">
         <v>15792132.49</v>
@@ -1831,13 +1831,13 @@
         <v>658970402.48000002</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" s="1">
         <v>3718781379.1399999</v>
@@ -1845,7 +1845,7 @@
     </row>
     <row r="14" spans="1:19">
       <c r="A14" s="4" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B14" s="6">
         <v>4421781180.9799995</v>
@@ -1869,7 +1869,7 @@
         <v>364277476.80000001</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" s="6">
         <v>14715613.23</v>
@@ -1890,13 +1890,13 @@
         <v>704367424.54999995</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" s="1">
         <v>3685574388.1700001</v>
@@ -1904,7 +1904,7 @@
     </row>
     <row r="15" spans="1:19">
       <c r="A15" s="4" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B15" s="6">
         <v>4777286303.5699997</v>
@@ -1928,7 +1928,7 @@
         <v>371038416.22000003</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" s="6">
         <v>-6227883.1100000003</v>
@@ -1949,13 +1949,13 @@
         <v>692239430.98000002</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" s="1">
         <v>3877997480.2199998</v>
@@ -1963,7 +1963,7 @@
     </row>
     <row r="16" spans="1:19">
       <c r="A16" s="4" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B16" s="6">
         <v>4864847110.5699997</v>
@@ -1987,7 +1987,7 @@
         <v>388404258.05000001</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" s="6">
         <v>-28380158.050000001</v>
@@ -2008,13 +2008,13 @@
         <v>741339904.29999995</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" s="1">
         <v>4075194534.8200002</v>
@@ -2022,7 +2022,7 @@
     </row>
     <row r="17" spans="1:19">
       <c r="A17" s="4" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B17" s="6">
         <v>4824945641.8100004</v>
@@ -2046,7 +2046,7 @@
         <v>386328052.08999997</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" s="6">
         <v>2385123.2599999998</v>
@@ -2067,13 +2067,13 @@
         <v>674377518.39999998</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" s="1">
         <v>4045951962.9499998</v>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="18" spans="1:19">
       <c r="A18" s="4" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B18" s="6">
         <v>5172624259.0799999</v>
@@ -2105,7 +2105,7 @@
         <v>382822271.44</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" s="6">
         <v>237113485.28</v>
@@ -2126,13 +2126,13 @@
         <v>701484254.82000005</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" s="1">
         <v>4374064889.75</v>
@@ -2140,7 +2140,7 @@
     </row>
     <row r="19" spans="1:19">
       <c r="A19" s="4" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B19" s="6">
         <v>4500844267.8599997</v>
@@ -2164,7 +2164,7 @@
         <v>382785707.95999998</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" s="6">
         <v>-244526490.25999999</v>
@@ -2185,13 +2185,13 @@
         <v>728366045.01999998</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" s="1">
         <v>3691731003.8000002</v>
@@ -2199,7 +2199,7 @@
     </row>
     <row r="20" spans="1:19">
       <c r="A20" s="4" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B20" s="6">
         <v>6220002918.9200001</v>
@@ -2223,7 +2223,7 @@
         <v>383453470.17000002</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="6">
         <v>198551755.03</v>
@@ -2244,13 +2244,13 @@
         <v>683785444.92999995</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" s="1">
         <v>5396274800.04</v>
@@ -2258,7 +2258,7 @@
     </row>
     <row r="21" spans="1:19">
       <c r="A21" s="4" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B21" s="6">
         <v>8453023582.3500004</v>
@@ -2282,7 +2282,7 @@
         <v>732984081.52999997</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" s="6">
         <v>-199985302.05000001</v>
@@ -2303,13 +2303,13 @@
         <v>1600259099.98</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" s="1">
         <v>6551552521.8500004</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="22" spans="1:19">
       <c r="A22" s="4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B22" s="6">
         <v>5142335256.0799999</v>
@@ -2341,10 +2341,10 @@
         <v>374100158.01999998</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
         <v>679520374.50999999</v>
@@ -2362,13 +2362,13 @@
         <v>651358951.58000004</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="1">
         <v>2147182.7400000002</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" s="1">
         <v>4462814881.5699997</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="23" spans="1:19">
       <c r="A23" s="4" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B23" s="6">
         <v>4691575185.7299995</v>
@@ -2400,10 +2400,10 @@
         <v>399899042.58999997</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
         <v>1002600580.0700001</v>
@@ -2421,13 +2421,13 @@
         <v>940535228.89999998</v>
       </c>
       <c r="P23" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="1">
         <v>2382729.06</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" s="1">
         <v>3688974605.6599998</v>
@@ -2435,7 +2435,7 @@
     </row>
     <row r="24" spans="1:19">
       <c r="A24" s="4" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B24" s="6">
         <v>4883599518.96</v>
@@ -2459,7 +2459,7 @@
         <v>383958166.20999998</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="6">
         <v>23029.97</v>
@@ -2480,13 +2480,13 @@
         <v>745467089.14999998</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="1">
         <v>2574085.14</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" s="1">
         <v>4076227440.9000001</v>
@@ -2494,7 +2494,7 @@
     </row>
     <row r="25" spans="1:19">
       <c r="A25" s="4" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B25" s="6">
         <v>4984015573.8199997</v>
@@ -2518,7 +2518,7 @@
         <v>387384947.72000003</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" s="6">
         <v>35039362.170000002</v>
@@ -2539,13 +2539,13 @@
         <v>817641788.14999998</v>
       </c>
       <c r="P25" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="1">
         <v>2289849.5699999998</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" s="1">
         <v>4127357675.6799998</v>
@@ -2553,7 +2553,7 @@
     </row>
     <row r="26" spans="1:19">
       <c r="A26" s="4" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B26" s="6">
         <v>5007946385.5699997</v>
@@ -2577,7 +2577,7 @@
         <v>383916817.05000001</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" s="6">
         <v>15621425.720000001</v>
@@ -2598,13 +2598,13 @@
         <v>840893745.90999997</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="1">
         <v>2203034.6</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" s="1">
         <v>4129768343</v>
@@ -2612,7 +2612,7 @@
     </row>
     <row r="27" spans="1:19">
       <c r="A27" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B27" s="6">
         <v>4993844224.0299997</v>
@@ -2636,7 +2636,7 @@
         <v>384091230.54000002</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" s="6">
         <v>-19757078.890000001</v>
@@ -2657,13 +2657,13 @@
         <v>804268379.27999997</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="1">
         <v>2244464.7000000002</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" s="1">
         <v>4106967202.4499998</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="28" spans="1:19">
       <c r="A28" s="4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B28" s="6">
         <v>5138995524.54</v>
@@ -2695,7 +2695,7 @@
         <v>389431106.86000001</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" s="6">
         <v>-20259400.460000001</v>
@@ -2716,13 +2716,13 @@
         <v>855701130.59000003</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="1">
         <v>2316564.1800000002</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" s="1">
         <v>4265137651.1799998</v>
@@ -2730,7 +2730,7 @@
     </row>
     <row r="29" spans="1:19">
       <c r="A29" s="4" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B29" s="6">
         <v>5030147335.2799997</v>
@@ -2754,7 +2754,7 @@
         <v>397068140.05000001</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" s="6">
         <v>38352468.380000003</v>
@@ -2775,13 +2775,13 @@
         <v>848693371.51999998</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="1">
         <v>2402954.91</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" s="1">
         <v>4160740958.29</v>
@@ -2789,7 +2789,7 @@
     </row>
     <row r="30" spans="1:19">
       <c r="A30" s="4" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B30" s="6">
         <v>5145331835.1300001</v>
@@ -2813,7 +2813,7 @@
         <v>405422540.48000002</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" s="6">
         <v>203091901.44</v>
@@ -2834,13 +2834,13 @@
         <v>790834769.98000002</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q30">
         <v>2402203.4</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30">
         <v>4346921458.4800005</v>
@@ -2848,7 +2848,7 @@
     </row>
     <row r="31" spans="1:19">
       <c r="A31" s="4" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B31" s="6">
         <v>5045992382.8700008</v>
@@ -2872,7 +2872,7 @@
         <v>396854653.42000002</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="6">
         <v>-182049373.91</v>
@@ -2893,13 +2893,13 @@
         <v>888983305.42999995</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q31">
         <v>2324597.75</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31">
         <v>4111275116.9500008</v>
@@ -2907,7 +2907,7 @@
     </row>
     <row r="32" spans="1:19">
       <c r="A32" s="4" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B32" s="6">
         <v>6426921051.710001</v>
@@ -2931,7 +2931,7 @@
         <v>387857753.36000001</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" s="6">
         <v>-52552996.479999997</v>
@@ -2952,13 +2952,13 @@
         <v>798717481.44000006</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q32">
         <v>2260710.5699999998</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32">
         <v>5466585034.5300007</v>
@@ -2966,7 +2966,7 @@
     </row>
     <row r="33" spans="1:19">
       <c r="A33" s="4" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B33" s="6">
         <v>9000020094.9299984</v>
@@ -2990,7 +2990,7 @@
         <v>757076509.19000006</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" s="6">
         <v>-17509337.940000001</v>
@@ -3011,13 +3011,13 @@
         <v>1755018355.47</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q33">
         <v>2223410.89</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33">
         <v>6924569552.0499983</v>

--- a/upload/despesa_pessoal_mensal.xlsx
+++ b/upload/despesa_pessoal_mensal.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C5CADD2-5573-484D-98D7-89CD373F7D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBDAAE12-2D7A-4A65-B5B6-23196EC8BE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19755" yWindow="0" windowWidth="18645" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="despesa_pessoal_mensal" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="69">
   <si>
     <t xml:space="preserve"> -   </t>
   </si>
@@ -188,6 +201,45 @@
   </si>
   <si>
     <t>abr-23</t>
+  </si>
+  <si>
+    <t>jan-22</t>
+  </si>
+  <si>
+    <t>fev-22</t>
+  </si>
+  <si>
+    <t>mar-22</t>
+  </si>
+  <si>
+    <t>abr-22</t>
+  </si>
+  <si>
+    <t>mai-22</t>
+  </si>
+  <si>
+    <t>jun-22</t>
+  </si>
+  <si>
+    <t>jul-22</t>
+  </si>
+  <si>
+    <t>ago-22</t>
+  </si>
+  <si>
+    <t>set-22</t>
+  </si>
+  <si>
+    <t>out-22</t>
+  </si>
+  <si>
+    <t>nov-22</t>
+  </si>
+  <si>
+    <t>dez-22</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -1066,7 +1118,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S16388"/>
+  <dimension ref="A1:S16400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.140625" style="6" customWidth="1"/>
@@ -1150,49 +1202,49 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B2" s="6">
-        <v>4281897002.4000001</v>
+        <v>3698856561.8800001</v>
       </c>
       <c r="C2" s="6">
-        <v>2242459602.27</v>
+        <v>1896887100.53</v>
       </c>
       <c r="D2" s="6">
-        <v>1808558295.75</v>
+        <v>1550340861.02</v>
       </c>
       <c r="E2" s="6">
-        <v>433901306.51999998</v>
+        <v>346546239.50999999</v>
       </c>
       <c r="F2" s="6">
-        <v>2032530414.95</v>
+        <v>1774313455.27</v>
       </c>
       <c r="G2" s="6">
-        <v>1678302234.8499999</v>
+        <v>1459545748.3</v>
       </c>
       <c r="H2" s="6">
-        <v>354228180.10000002</v>
-      </c>
-      <c r="I2" s="6">
-        <v>1079.67</v>
+        <v>314767706.97000003</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="J2" s="6">
-        <v>6905905.5099999998</v>
-      </c>
-      <c r="K2" s="1">
-        <v>807861869.01999998</v>
-      </c>
-      <c r="L2" s="1">
-        <v>270185.84000000003</v>
-      </c>
-      <c r="M2" s="1">
-        <v>31494.49</v>
-      </c>
-      <c r="N2" s="1">
-        <v>19758537.739999998</v>
-      </c>
-      <c r="O2" s="1">
-        <v>787801650.95000005</v>
+        <v>27656006.079999998</v>
+      </c>
+      <c r="K2" s="6">
+        <v>525023112.38999999</v>
+      </c>
+      <c r="L2" s="6">
+        <v>1245.76</v>
+      </c>
+      <c r="M2" s="6">
+        <v>1019362.32</v>
+      </c>
+      <c r="N2" s="6">
+        <v>3245836.25</v>
+      </c>
+      <c r="O2" s="6">
+        <v>520756668.06</v>
       </c>
       <c r="P2" s="6" t="s">
         <v>0</v>
@@ -1204,54 +1256,54 @@
         <v>0</v>
       </c>
       <c r="S2" s="1">
-        <v>3474035133.3800001</v>
+        <v>3173833449.4899998</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B3" s="6">
-        <v>3979615919.6199999</v>
+        <v>3575473472.1999998</v>
       </c>
       <c r="C3" s="6">
-        <v>2031021877.8599999</v>
+        <v>1775417530.71</v>
       </c>
       <c r="D3" s="6">
-        <v>1621951928.02</v>
+        <v>1442391162.3099999</v>
       </c>
       <c r="E3" s="6">
-        <v>409069949.83999997</v>
+        <v>333026368.39999998</v>
       </c>
       <c r="F3" s="6">
-        <v>1933378706.72</v>
+        <v>1791793878.04</v>
       </c>
       <c r="G3" s="6">
-        <v>1583233222.2</v>
+        <v>1471496315.3499999</v>
       </c>
       <c r="H3" s="6">
-        <v>350145484.51999998</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="J3" s="6">
-        <v>15215335.039999999</v>
+        <v>320297562.69</v>
+      </c>
+      <c r="I3" t="s">
+        <v>68</v>
+      </c>
+      <c r="J3" s="1">
+        <v>8262063.4500000002</v>
       </c>
       <c r="K3" s="1">
-        <v>543144933.39999998</v>
+        <v>606690441.07000005</v>
       </c>
       <c r="L3" s="1">
-        <v>6418722.8200000003</v>
+        <v>347827.42</v>
       </c>
       <c r="M3" s="1">
-        <v>7274498.3499999996</v>
+        <v>21338272.039999999</v>
       </c>
       <c r="N3" s="1">
-        <v>3927591.05</v>
+        <v>10737457.15</v>
       </c>
       <c r="O3" s="1">
-        <v>525524121.18000001</v>
+        <v>574266884.46000004</v>
       </c>
       <c r="P3" s="6" t="s">
         <v>0</v>
@@ -1263,54 +1315,54 @@
         <v>0</v>
       </c>
       <c r="S3" s="1">
-        <v>3436470986.2199998</v>
+        <v>2968783031.1300001</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B4" s="6">
-        <v>4107503828.8400002</v>
+        <v>3594524466.5999999</v>
       </c>
       <c r="C4" s="6">
-        <v>2060260691.47</v>
+        <v>1787614286.2</v>
       </c>
       <c r="D4" s="6">
-        <v>1700288006.78</v>
+        <v>1483558348.72</v>
       </c>
       <c r="E4" s="6">
-        <v>359972684.69</v>
+        <v>304055937.48000002</v>
       </c>
       <c r="F4" s="6">
-        <v>1976898290.3099999</v>
+        <v>1766055061.6500001</v>
       </c>
       <c r="G4" s="6">
-        <v>1629163049.9100001</v>
+        <v>1457674854.95</v>
       </c>
       <c r="H4" s="6">
-        <v>347735240.39999998</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="J4" s="6">
-        <v>70344847.060000002</v>
+        <v>308380206.69999999</v>
+      </c>
+      <c r="I4" s="1">
+        <v>2332.92</v>
+      </c>
+      <c r="J4" s="1">
+        <v>40852785.829999998</v>
       </c>
       <c r="K4" s="1">
-        <v>524734877.36000001</v>
+        <v>448068835.75999999</v>
       </c>
       <c r="L4" s="1">
-        <v>6253467.3899999997</v>
+        <v>1946198.31</v>
       </c>
       <c r="M4" s="1">
-        <v>58287462.490000002</v>
+        <v>23142299.899999999</v>
       </c>
       <c r="N4" s="1">
-        <v>2389979.4</v>
+        <v>1860372.01</v>
       </c>
       <c r="O4" s="1">
-        <v>457803968.07999998</v>
+        <v>421119965.54000002</v>
       </c>
       <c r="P4" s="6" t="s">
         <v>0</v>
@@ -1322,54 +1374,54 @@
         <v>0</v>
       </c>
       <c r="S4" s="1">
-        <v>3582768951.48</v>
+        <v>3146455630.8400002</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B5" s="6">
-        <v>4144166524.6100001</v>
+        <v>4211724456.0599999</v>
       </c>
       <c r="C5" s="6">
-        <v>2174000477.4899998</v>
+        <v>2049635792.5</v>
       </c>
       <c r="D5" s="6">
-        <v>1722178728.3599999</v>
+        <v>1704875164.8199999</v>
       </c>
       <c r="E5" s="6">
-        <v>451821749.13</v>
+        <v>344760627.68000001</v>
       </c>
       <c r="F5" s="6">
-        <v>1993250701.03</v>
+        <v>1938263197.8199999</v>
       </c>
       <c r="G5" s="6">
-        <v>1643964031.28</v>
+        <v>1600487400.1400001</v>
       </c>
       <c r="H5" s="6">
-        <v>349286669.75</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="J5" s="6">
-        <v>-23084653.91</v>
+        <v>337775797.68000001</v>
+      </c>
+      <c r="I5">
+        <v>244.92</v>
+      </c>
+      <c r="J5" s="1">
+        <v>223825220.81999999</v>
       </c>
       <c r="K5" s="1">
-        <v>755158443.24000001</v>
+        <v>429700183.51999998</v>
       </c>
       <c r="L5" s="1">
-        <v>5834303.2599999998</v>
+        <v>4276732.84</v>
       </c>
       <c r="M5" s="1">
-        <v>81964753.25</v>
+        <v>57346257.659999996</v>
       </c>
       <c r="N5" s="1">
-        <v>4828789.1900000004</v>
+        <v>3922835.3</v>
       </c>
       <c r="O5" s="1">
-        <v>662530597.53999996</v>
+        <v>364154357.72000003</v>
       </c>
       <c r="P5" s="6" t="s">
         <v>0</v>
@@ -1381,54 +1433,54 @@
         <v>0</v>
       </c>
       <c r="S5" s="1">
-        <v>3389008081.3699999</v>
+        <v>3782024272.54</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="B6" s="6">
-        <v>4102729301.0700002</v>
+        <v>4976493293.9700003</v>
       </c>
       <c r="C6" s="6">
-        <v>2140504369.77</v>
+        <v>2566815994.1399999</v>
       </c>
       <c r="D6" s="6">
-        <v>1687546023.9000001</v>
+        <v>2096513667.6300001</v>
       </c>
       <c r="E6" s="6">
-        <v>452958345.87</v>
+        <v>470302326.50999999</v>
       </c>
       <c r="F6" s="6">
-        <v>2003348649.7</v>
+        <v>2391649900.2600002</v>
       </c>
       <c r="G6" s="6">
-        <v>1644268537.5899999</v>
+        <v>1995968705.8099999</v>
       </c>
       <c r="H6" s="6">
-        <v>359080112.11000001</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="J6" s="6">
-        <v>-41123718.399999999</v>
+        <v>395681194.44999999</v>
+      </c>
+      <c r="I6" t="s">
+        <v>68</v>
+      </c>
+      <c r="J6" s="1">
+        <v>18027399.57</v>
       </c>
       <c r="K6" s="1">
-        <v>723615616.88</v>
+        <v>627580101.67999995</v>
       </c>
       <c r="L6" s="1">
-        <v>7870443.2300000004</v>
+        <v>26952.7</v>
       </c>
       <c r="M6" s="1">
-        <v>20756412.309999999</v>
+        <v>37257449.710000001</v>
       </c>
       <c r="N6" s="1">
-        <v>5339508.57</v>
+        <v>2412579.4500000002</v>
       </c>
       <c r="O6" s="1">
-        <v>689649252.76999998</v>
+        <v>587883119.82000005</v>
       </c>
       <c r="P6" s="6" t="s">
         <v>0</v>
@@ -1440,54 +1492,54 @@
         <v>0</v>
       </c>
       <c r="S6" s="1">
-        <v>3379113684.1900001</v>
+        <v>4348913192.29</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="B7" s="6">
-        <v>4134753101.8000002</v>
+        <v>4085962957.9000001</v>
       </c>
       <c r="C7" s="6">
-        <v>2099849560.8900001</v>
+        <v>2161370423.02</v>
       </c>
       <c r="D7" s="6">
-        <v>1665572922.3099999</v>
+        <v>1733942179.8699999</v>
       </c>
       <c r="E7" s="6">
-        <v>434276638.57999998</v>
+        <v>427428243.14999998</v>
       </c>
       <c r="F7" s="6">
-        <v>1992119013.45</v>
+        <v>1943408389.6900001</v>
       </c>
       <c r="G7" s="6">
-        <v>1645496775.9400001</v>
+        <v>1596794777.1099999</v>
       </c>
       <c r="H7" s="6">
-        <v>346622237.50999999</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="J7" s="6">
-        <v>42784527.460000001</v>
+        <v>346613612.57999998</v>
+      </c>
+      <c r="I7" t="s">
+        <v>68</v>
+      </c>
+      <c r="J7" s="1">
+        <v>-18815854.809999999</v>
       </c>
       <c r="K7" s="1">
-        <v>685281756.13</v>
+        <v>764780504.5</v>
       </c>
       <c r="L7" s="1">
-        <v>8450436.4100000001</v>
+        <v>6823967.0300000003</v>
       </c>
       <c r="M7" s="1">
-        <v>23983568.890000001</v>
+        <v>23207933.91</v>
       </c>
       <c r="N7" s="1">
-        <v>1028568.67</v>
+        <v>1290105.29</v>
       </c>
       <c r="O7" s="1">
-        <v>651819182.15999997</v>
+        <v>733458498.26999998</v>
       </c>
       <c r="P7" s="6" t="s">
         <v>0</v>
@@ -1499,54 +1551,54 @@
         <v>0</v>
       </c>
       <c r="S7" s="1">
-        <v>3449471345.6700001</v>
+        <v>3321182453.4000001</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="B8" s="6">
-        <v>4365127462.1800003</v>
+        <v>4159264473.5999999</v>
       </c>
       <c r="C8" s="6">
-        <v>2259466362.0500002</v>
+        <v>2148886396.4899998</v>
       </c>
       <c r="D8" s="6">
-        <v>1809819475.0899999</v>
+        <v>1740125798.51</v>
       </c>
       <c r="E8" s="6">
-        <v>449646886.95999998</v>
+        <v>408760597.98000002</v>
       </c>
       <c r="F8" s="6">
-        <v>2075366468.45</v>
+        <v>1954812411.8399999</v>
       </c>
       <c r="G8" s="6">
-        <v>1718520998.98</v>
+        <v>1609372155.7</v>
       </c>
       <c r="H8" s="6">
-        <v>356845469.47000003</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="J8" s="6">
-        <v>30294631.68</v>
+        <v>345440256.13999999</v>
+      </c>
+      <c r="I8" t="s">
+        <v>68</v>
+      </c>
+      <c r="J8" s="1">
+        <v>55565665.270000003</v>
       </c>
       <c r="K8" s="1">
-        <v>684125829.91999996</v>
+        <v>605990449.92999995</v>
       </c>
       <c r="L8" s="1">
-        <v>7819785.2300000004</v>
+        <v>4055399.45</v>
       </c>
       <c r="M8" s="1">
-        <v>30044886.190000001</v>
+        <v>32637440.48</v>
       </c>
       <c r="N8" s="1">
-        <v>457197.35</v>
+        <v>571468.09</v>
       </c>
       <c r="O8" s="1">
-        <v>645803961.14999998</v>
+        <v>568726141.90999997</v>
       </c>
       <c r="P8" s="6" t="s">
         <v>0</v>
@@ -1558,54 +1610,54 @@
         <v>0</v>
       </c>
       <c r="S8" s="1">
-        <v>3681001632.2600002</v>
+        <v>3553274023.6700001</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="B9" s="6">
-        <v>4749291854.6000004</v>
+        <v>4096482229.1799998</v>
       </c>
       <c r="C9" s="6">
-        <v>2259505800.0900002</v>
+        <v>2186677945.27</v>
       </c>
       <c r="D9" s="6">
-        <v>1874334270.0599999</v>
+        <v>1775180088.6500001</v>
       </c>
       <c r="E9" s="6">
-        <v>385171530.02999997</v>
+        <v>411497856.62</v>
       </c>
       <c r="F9" s="6">
-        <v>2218535447.0999999</v>
+        <v>1948247036.55</v>
       </c>
       <c r="G9" s="6">
-        <v>1856755501.74</v>
+        <v>1606539854.8199999</v>
       </c>
       <c r="H9" s="6">
-        <v>361779945.36000001</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="J9" s="6">
-        <v>271250607.41000003</v>
+        <v>341707181.73000002</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J9" s="1">
+        <v>-38442752.640000001</v>
       </c>
       <c r="K9" s="1">
-        <v>724614514.5</v>
+        <v>759865251.65999997</v>
       </c>
       <c r="L9" s="1">
-        <v>7475374.0199999996</v>
+        <v>7780961.0099999998</v>
       </c>
       <c r="M9" s="1">
-        <v>20834433.260000002</v>
+        <v>59607656.200000003</v>
       </c>
       <c r="N9" s="1">
-        <v>4478674.43</v>
+        <v>1005004.33</v>
       </c>
       <c r="O9" s="1">
-        <v>691826032.78999996</v>
+        <v>691471630.12</v>
       </c>
       <c r="P9" s="6" t="s">
         <v>0</v>
@@ -1617,54 +1669,54 @@
         <v>0</v>
       </c>
       <c r="S9" s="1">
-        <v>4024677340.0999999</v>
+        <v>3336616977.52</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="B10" s="6">
-        <v>4737908259.96</v>
+        <v>3954239678.3899999</v>
       </c>
       <c r="C10" s="6">
-        <v>2851003205.27</v>
+        <v>1952424034.01</v>
       </c>
       <c r="D10" s="6">
-        <v>2243825676.77</v>
+        <v>1551261620.5799999</v>
       </c>
       <c r="E10" s="6">
-        <v>607177528.5</v>
+        <v>401162413.43000001</v>
       </c>
       <c r="F10" s="6">
-        <v>2237312619.1199999</v>
+        <v>1955979847.47</v>
       </c>
       <c r="G10" s="6">
-        <v>1882024345.96</v>
+        <v>1612211222.6800001</v>
       </c>
       <c r="H10" s="6">
-        <v>355288273.16000003</v>
+        <v>343768624.79000002</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>0</v>
       </c>
       <c r="J10" s="6">
-        <v>-350407564.43000001</v>
+        <v>45835796.909999996</v>
       </c>
       <c r="K10" s="1">
-        <v>685868475.12</v>
+        <v>432947518.44</v>
       </c>
       <c r="L10" s="1">
-        <v>7695040.1399999997</v>
+        <v>6049121.0599999996</v>
       </c>
       <c r="M10" s="1">
-        <v>15633243.25</v>
+        <v>25972129.600000001</v>
       </c>
       <c r="N10" s="1">
-        <v>104457802.92</v>
+        <v>429755.06</v>
       </c>
       <c r="O10" s="1">
-        <v>558082388.80999994</v>
+        <v>400496512.72000003</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>0</v>
@@ -1676,54 +1728,54 @@
         <v>0</v>
       </c>
       <c r="S10" s="1">
-        <v>4052039784.8400002</v>
+        <v>3521292159.9499998</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="B11" s="6">
-        <v>4704099845.4399996</v>
+        <v>4097618070.5700002</v>
       </c>
       <c r="C11" s="6">
-        <v>2478033756.71</v>
+        <v>1954998392.5899999</v>
       </c>
       <c r="D11" s="6">
-        <v>1967011743.4000001</v>
+        <v>1582029323.6800001</v>
       </c>
       <c r="E11" s="6">
-        <v>511022013.31</v>
+        <v>372969068.91000003</v>
       </c>
       <c r="F11" s="6">
-        <v>2222932727.5900002</v>
+        <v>2007866067.3199999</v>
       </c>
       <c r="G11" s="6">
-        <v>1868027079.53</v>
+        <v>1654339869.49</v>
       </c>
       <c r="H11" s="6">
-        <v>354905648.06</v>
+        <v>353526197.82999998</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>0</v>
       </c>
       <c r="J11" s="6">
-        <v>3133361.14</v>
+        <v>134753610.66</v>
       </c>
       <c r="K11" s="1">
-        <v>572925761.97000003</v>
+        <v>809751735.03999996</v>
       </c>
       <c r="L11" s="1">
-        <v>15098619.939999999</v>
+        <v>6156475.8700000001</v>
       </c>
       <c r="M11" s="1">
-        <v>26393500.09</v>
+        <v>47646169.119999997</v>
       </c>
       <c r="N11" s="1">
-        <v>25306759.550000001</v>
+        <v>322736.33</v>
       </c>
       <c r="O11" s="1">
-        <v>506126882.38999999</v>
+        <v>755626353.72000003</v>
       </c>
       <c r="P11" s="6" t="s">
         <v>0</v>
@@ -1735,54 +1787,54 @@
         <v>0</v>
       </c>
       <c r="S11" s="1">
-        <v>4131174083.4699998</v>
+        <v>3287866335.5300002</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="B12" s="6">
-        <v>5529623295.6599998</v>
+        <v>7573608944.5100002</v>
       </c>
       <c r="C12" s="6">
-        <v>2785192412.8800001</v>
+        <v>4003667989.7399998</v>
       </c>
       <c r="D12" s="6">
-        <v>2321355687.52</v>
+        <v>3270050770.23</v>
       </c>
       <c r="E12" s="6">
-        <v>463836725.36000001</v>
+        <v>733617219.50999999</v>
       </c>
       <c r="F12" s="6">
-        <v>2504665391.9499998</v>
+        <v>3474753170.4699998</v>
       </c>
       <c r="G12" s="6">
-        <v>2148295147.54</v>
+        <v>3115811681.29</v>
       </c>
       <c r="H12" s="6">
-        <v>356370244.41000003</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>0</v>
+        <v>358941489.18000001</v>
+      </c>
+      <c r="I12" s="6">
+        <v>3802.95</v>
       </c>
       <c r="J12" s="6">
-        <v>239765490.83000001</v>
+        <v>95183981.349999994</v>
       </c>
       <c r="K12" s="1">
-        <v>811508446.20000005</v>
+        <v>1399378893.46</v>
       </c>
       <c r="L12" s="1">
-        <v>17749943.550000001</v>
+        <v>15476083.92</v>
       </c>
       <c r="M12" s="1">
-        <v>150022534.02000001</v>
+        <v>28192033.079999998</v>
       </c>
       <c r="N12" s="1">
-        <v>5819731.5700000003</v>
+        <v>1410449.85</v>
       </c>
       <c r="O12" s="1">
-        <v>637916237.05999994</v>
+        <v>1354300326.6099999</v>
       </c>
       <c r="P12" s="6" t="s">
         <v>0</v>
@@ -1794,54 +1846,54 @@
         <v>0</v>
       </c>
       <c r="S12" s="1">
-        <v>4718114849.46</v>
+        <v>6174230051.0500002</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="B13" s="6">
-        <v>8243411483.1899996</v>
+        <v>4963234088.5699997</v>
       </c>
       <c r="C13" s="6">
-        <v>4450804743.0699997</v>
+        <v>2960287152.6500001</v>
       </c>
       <c r="D13" s="6">
-        <v>3531477755.5</v>
+        <v>2358654121.25</v>
       </c>
       <c r="E13" s="6">
-        <v>919326987.57000005</v>
+        <v>601633031.39999998</v>
       </c>
       <c r="F13" s="6">
-        <v>3685098027.6599998</v>
+        <v>2389049593.0500002</v>
       </c>
       <c r="G13" s="6">
-        <v>2994281171.8099999</v>
+        <v>1734086733.1099999</v>
       </c>
       <c r="H13" s="6">
-        <v>690816855.85000002</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>0</v>
+        <v>654962859.94000006</v>
+      </c>
+      <c r="I13" s="6">
+        <v>3219.54</v>
       </c>
       <c r="J13" s="6">
-        <v>107508712.45999999</v>
+        <v>-1204937774.9200001</v>
       </c>
       <c r="K13" s="1">
-        <v>2072486830.4400001</v>
+        <v>1322005792.52</v>
       </c>
       <c r="L13" s="1">
-        <v>10722630.08</v>
+        <v>12781731.51</v>
       </c>
       <c r="M13" s="1">
-        <v>453644334.55000001</v>
+        <v>602468887.46000004</v>
       </c>
       <c r="N13" s="1">
-        <v>19216057.120000001</v>
+        <v>12324993.07</v>
       </c>
       <c r="O13" s="1">
-        <v>1588903808.6900001</v>
+        <v>694430180.48000002</v>
       </c>
       <c r="P13" s="6" t="s">
         <v>0</v>
@@ -1853,54 +1905,54 @@
         <v>0</v>
       </c>
       <c r="S13" s="1">
-        <v>6170924652.75</v>
+        <v>3641228296.0500002</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>18</v>
+      <c r="A14" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="B14" s="6">
-        <v>4360614719.8500004</v>
+        <v>4281897002.4000001</v>
       </c>
       <c r="C14" s="6">
-        <v>2308373595.3499999</v>
+        <v>2242459602.27</v>
       </c>
       <c r="D14" s="6">
-        <v>1860038435.97</v>
+        <v>1808558295.75</v>
       </c>
       <c r="E14" s="6">
-        <v>448335159.38</v>
+        <v>433901306.51999998</v>
       </c>
       <c r="F14" s="6">
-        <v>2047085583.4400001</v>
+        <v>2032530414.95</v>
       </c>
       <c r="G14" s="6">
-        <v>1680765899.24</v>
+        <v>1678302234.8499999</v>
       </c>
       <c r="H14" s="6">
-        <v>366319684.19999999</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>0</v>
+        <v>354228180.10000002</v>
+      </c>
+      <c r="I14" s="6">
+        <v>1079.67</v>
       </c>
       <c r="J14" s="6">
-        <v>5155541.0599999996</v>
+        <v>6905905.5099999998</v>
       </c>
       <c r="K14" s="1">
-        <v>683044152.41999996</v>
+        <v>807861869.01999998</v>
       </c>
       <c r="L14" s="1">
-        <v>308745.77</v>
+        <v>270185.84000000003</v>
       </c>
       <c r="M14" s="1">
-        <v>8093864.46</v>
+        <v>31494.49</v>
       </c>
       <c r="N14" s="1">
-        <v>18501571.800000001</v>
+        <v>19758537.739999998</v>
       </c>
       <c r="O14" s="1">
-        <v>656139970.38999999</v>
+        <v>787801650.95000005</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>0</v>
@@ -1912,54 +1964,54 @@
         <v>0</v>
       </c>
       <c r="S14" s="1">
-        <v>3677570567.4299998</v>
+        <v>3474035133.3800001</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>19</v>
+      <c r="A15" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="B15" s="6">
-        <v>4542452747.0600004</v>
+        <v>3979615919.6199999</v>
       </c>
       <c r="C15" s="6">
-        <v>2421454854.4899998</v>
+        <v>2031021877.8599999</v>
       </c>
       <c r="D15" s="6">
-        <v>1937483038.6300001</v>
+        <v>1621951928.02</v>
       </c>
       <c r="E15" s="6">
-        <v>483971815.86000001</v>
+        <v>409069949.83999997</v>
       </c>
       <c r="F15" s="6">
-        <v>2124792912.6099999</v>
+        <v>1933378706.72</v>
       </c>
       <c r="G15" s="6">
-        <v>1768421702.01</v>
+        <v>1583233222.2</v>
       </c>
       <c r="H15" s="6">
-        <v>356371210.60000002</v>
+        <v>350145484.51999998</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>0</v>
       </c>
       <c r="J15" s="6">
-        <v>-3795020.04</v>
+        <v>15215335.039999999</v>
       </c>
       <c r="K15" s="1">
-        <v>778229360.70000005</v>
+        <v>543144933.39999998</v>
       </c>
       <c r="L15" s="1">
-        <v>10543654.33</v>
+        <v>6418722.8200000003</v>
       </c>
       <c r="M15" s="1">
-        <v>61631938.899999999</v>
+        <v>7274498.3499999996</v>
       </c>
       <c r="N15" s="1">
-        <v>6392197.6200000001</v>
+        <v>3927591.05</v>
       </c>
       <c r="O15" s="1">
-        <v>699661569.85000002</v>
+        <v>525524121.18000001</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>0</v>
@@ -1971,54 +2023,54 @@
         <v>0</v>
       </c>
       <c r="S15" s="1">
-        <v>3764223386.3600001</v>
+        <v>3436470986.2199998</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>20</v>
+      <c r="A16" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="B16" s="6">
-        <v>4382405735.6599998</v>
+        <v>4107503828.8400002</v>
       </c>
       <c r="C16" s="6">
-        <v>2281647247.4899998</v>
+        <v>2060260691.47</v>
       </c>
       <c r="D16" s="6">
-        <v>1821495612.3900001</v>
+        <v>1700288006.78</v>
       </c>
       <c r="E16" s="6">
-        <v>460151635.10000002</v>
+        <v>359972684.69</v>
       </c>
       <c r="F16" s="6">
-        <v>2091557285.01</v>
+        <v>1976898290.3099999</v>
       </c>
       <c r="G16" s="6">
-        <v>1726840987.8599999</v>
+        <v>1629163049.9100001</v>
       </c>
       <c r="H16" s="6">
-        <v>364716297.14999998</v>
+        <v>347735240.39999998</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>0</v>
       </c>
       <c r="J16" s="6">
-        <v>9201203.1600000001</v>
+        <v>70344847.060000002</v>
       </c>
       <c r="K16" s="1">
-        <v>751953354.75999999</v>
+        <v>524734877.36000001</v>
       </c>
       <c r="L16" s="1">
-        <v>8467968.6099999994</v>
+        <v>6253467.3899999997</v>
       </c>
       <c r="M16" s="1">
-        <v>16983642.210000001</v>
+        <v>58287462.490000002</v>
       </c>
       <c r="N16" s="1">
-        <v>6157522.7800000003</v>
+        <v>2389979.4</v>
       </c>
       <c r="O16" s="1">
-        <v>720344221.15999997</v>
+        <v>457803968.07999998</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>0</v>
@@ -2030,54 +2082,54 @@
         <v>0</v>
       </c>
       <c r="S16" s="1">
-        <v>3630452380.9000001</v>
+        <v>3582768951.48</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>23</v>
+      <c r="A17" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="B17" s="6">
-        <v>4408807782.6400003</v>
+        <v>4144166524.6100001</v>
       </c>
       <c r="C17" s="6">
-        <v>2321518043.4299998</v>
+        <v>2174000477.4899998</v>
       </c>
       <c r="D17" s="6">
-        <v>1851831129.55</v>
+        <v>1722178728.3599999</v>
       </c>
       <c r="E17" s="6">
-        <v>469686913.88</v>
+        <v>451821749.13</v>
       </c>
       <c r="F17" s="6">
-        <v>2071497606.72</v>
+        <v>1993250701.03</v>
       </c>
       <c r="G17" s="6">
-        <v>1706026430.8800001</v>
+        <v>1643964031.28</v>
       </c>
       <c r="H17" s="6">
-        <v>365471175.83999997</v>
+        <v>349286669.75</v>
       </c>
       <c r="I17" s="6" t="s">
         <v>0</v>
       </c>
       <c r="J17" s="6">
-        <v>15792132.49</v>
+        <v>-23084653.91</v>
       </c>
       <c r="K17" s="1">
-        <v>690026403.5</v>
+        <v>755158443.24000001</v>
       </c>
       <c r="L17" s="1">
-        <v>9081298.1500000004</v>
+        <v>5834303.2599999998</v>
       </c>
       <c r="M17" s="1">
-        <v>16368983.15</v>
+        <v>81964753.25</v>
       </c>
       <c r="N17" s="1">
-        <v>5605719.7199999997</v>
+        <v>4828789.1900000004</v>
       </c>
       <c r="O17" s="1">
-        <v>658970402.48000002</v>
+        <v>662530597.53999996</v>
       </c>
       <c r="P17" s="6" t="s">
         <v>0</v>
@@ -2089,54 +2141,54 @@
         <v>0</v>
       </c>
       <c r="S17" s="1">
-        <v>3718781379.1399999</v>
+        <v>3389008081.3699999</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B18" s="6">
-        <v>4421781180.9799995</v>
+        <v>4102729301.0700002</v>
       </c>
       <c r="C18" s="6">
-        <v>2313987463.6599998</v>
+        <v>2140504369.77</v>
       </c>
       <c r="D18" s="6">
-        <v>1842233676.97</v>
+        <v>1687546023.9000001</v>
       </c>
       <c r="E18" s="6">
-        <v>471753786.69</v>
+        <v>452958345.87</v>
       </c>
       <c r="F18" s="6">
-        <v>2093078104.0899999</v>
+        <v>2003348649.7</v>
       </c>
       <c r="G18" s="6">
-        <v>1728800627.29</v>
+        <v>1644268537.5899999</v>
       </c>
       <c r="H18" s="6">
-        <v>364277476.80000001</v>
+        <v>359080112.11000001</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>0</v>
       </c>
       <c r="J18" s="6">
-        <v>14715613.23</v>
+        <v>-41123718.399999999</v>
       </c>
       <c r="K18" s="1">
-        <v>736206792.80999994</v>
+        <v>723615616.88</v>
       </c>
       <c r="L18" s="1">
-        <v>8635039.0199999996</v>
+        <v>7870443.2300000004</v>
       </c>
       <c r="M18" s="1">
-        <v>17474533.399999999</v>
+        <v>20756412.309999999</v>
       </c>
       <c r="N18" s="1">
-        <v>5729795.8399999999</v>
+        <v>5339508.57</v>
       </c>
       <c r="O18" s="1">
-        <v>704367424.54999995</v>
+        <v>689649252.76999998</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>0</v>
@@ -2148,54 +2200,54 @@
         <v>0</v>
       </c>
       <c r="S18" s="1">
-        <v>3685574388.1700001</v>
+        <v>3379113684.1900001</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B19" s="6">
-        <v>4777286303.5699997</v>
+        <v>4134753101.8000002</v>
       </c>
       <c r="C19" s="6">
-        <v>2592886975.6999998</v>
+        <v>2099849560.8900001</v>
       </c>
       <c r="D19" s="6">
-        <v>2117705051.8299999</v>
+        <v>1665572922.3099999</v>
       </c>
       <c r="E19" s="6">
-        <v>475181923.87</v>
+        <v>434276638.57999998</v>
       </c>
       <c r="F19" s="6">
-        <v>2190627210.98</v>
+        <v>1992119013.45</v>
       </c>
       <c r="G19" s="6">
-        <v>1819588794.76</v>
+        <v>1645496775.9400001</v>
       </c>
       <c r="H19" s="6">
-        <v>371038416.22000003</v>
+        <v>346622237.50999999</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>0</v>
       </c>
       <c r="J19" s="6">
-        <v>-6227883.1100000003</v>
+        <v>42784527.460000001</v>
       </c>
       <c r="K19" s="1">
-        <v>899288823.35000002</v>
+        <v>685281756.13</v>
       </c>
       <c r="L19" s="1">
-        <v>1822807.66</v>
+        <v>8450436.4100000001</v>
       </c>
       <c r="M19" s="1">
-        <v>203655029.11000001</v>
+        <v>23983568.890000001</v>
       </c>
       <c r="N19" s="1">
-        <v>1571555.6</v>
+        <v>1028568.67</v>
       </c>
       <c r="O19" s="1">
-        <v>692239430.98000002</v>
+        <v>651819182.15999997</v>
       </c>
       <c r="P19" s="6" t="s">
         <v>0</v>
@@ -2207,54 +2259,54 @@
         <v>0</v>
       </c>
       <c r="S19" s="1">
-        <v>3877997480.2199998</v>
+        <v>3449471345.6700001</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B20" s="6">
-        <v>4864847110.5699997</v>
+        <v>4365127462.1800003</v>
       </c>
       <c r="C20" s="6">
-        <v>2610035008.9899998</v>
+        <v>2259466362.0500002</v>
       </c>
       <c r="D20" s="6">
-        <v>2092659098.79</v>
+        <v>1809819475.0899999</v>
       </c>
       <c r="E20" s="6">
-        <v>517375910.19999999</v>
+        <v>449646886.95999998</v>
       </c>
       <c r="F20" s="6">
-        <v>2283192259.6300001</v>
+        <v>2075366468.45</v>
       </c>
       <c r="G20" s="6">
-        <v>1894788001.5799999</v>
+        <v>1718520998.98</v>
       </c>
       <c r="H20" s="6">
-        <v>388404258.05000001</v>
+        <v>356845469.47000003</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>0</v>
       </c>
       <c r="J20" s="6">
-        <v>-28380158.050000001</v>
+        <v>30294631.68</v>
       </c>
       <c r="K20" s="1">
-        <v>789652575.75</v>
+        <v>684125829.91999996</v>
       </c>
       <c r="L20" s="1">
-        <v>1708149.44</v>
+        <v>7819785.2300000004</v>
       </c>
       <c r="M20" s="1">
-        <v>45116396.200000003</v>
+        <v>30044886.190000001</v>
       </c>
       <c r="N20" s="1">
-        <v>1488125.81</v>
+        <v>457197.35</v>
       </c>
       <c r="O20" s="1">
-        <v>741339904.29999995</v>
+        <v>645803961.14999998</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>0</v>
@@ -2266,54 +2318,54 @@
         <v>0</v>
       </c>
       <c r="S20" s="1">
-        <v>4075194534.8200002</v>
+        <v>3681001632.2600002</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B21" s="6">
-        <v>4824945641.8100004</v>
+        <v>4749291854.6000004</v>
       </c>
       <c r="C21" s="6">
-        <v>2565043071.4000001</v>
+        <v>2259505800.0900002</v>
       </c>
       <c r="D21" s="6">
-        <v>2056032621.1800001</v>
+        <v>1874334270.0599999</v>
       </c>
       <c r="E21" s="6">
-        <v>509010450.22000003</v>
+        <v>385171530.02999997</v>
       </c>
       <c r="F21" s="6">
-        <v>2257517447.1500001</v>
+        <v>2218535447.0999999</v>
       </c>
       <c r="G21" s="6">
-        <v>1871189395.0599999</v>
+        <v>1856755501.74</v>
       </c>
       <c r="H21" s="6">
-        <v>386328052.08999997</v>
+        <v>361779945.36000001</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>0</v>
       </c>
       <c r="J21" s="6">
-        <v>2385123.2599999998</v>
+        <v>271250607.41000003</v>
       </c>
       <c r="K21" s="1">
-        <v>778993678.86000001</v>
+        <v>724614514.5</v>
       </c>
       <c r="L21" s="1">
-        <v>2161969.98</v>
+        <v>7475374.0199999996</v>
       </c>
       <c r="M21" s="1">
-        <v>99261490.560000002</v>
+        <v>20834433.260000002</v>
       </c>
       <c r="N21" s="1">
-        <v>3192699.92</v>
+        <v>4478674.43</v>
       </c>
       <c r="O21" s="1">
-        <v>674377518.39999998</v>
+        <v>691826032.78999996</v>
       </c>
       <c r="P21" s="6" t="s">
         <v>0</v>
@@ -2325,54 +2377,54 @@
         <v>0</v>
       </c>
       <c r="S21" s="1">
-        <v>4045951962.9499998</v>
+        <v>4024677340.0999999</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B22" s="6">
-        <v>5172624259.0799999</v>
+        <v>4737908259.96</v>
       </c>
       <c r="C22" s="6">
-        <v>2687215011.2399998</v>
+        <v>2851003205.27</v>
       </c>
       <c r="D22" s="6">
-        <v>2207789161.1700001</v>
+        <v>2243825676.77</v>
       </c>
       <c r="E22" s="6">
-        <v>479425850.06999999</v>
+        <v>607177528.5</v>
       </c>
       <c r="F22" s="6">
-        <v>2248295762.5599999</v>
+        <v>2237312619.1199999</v>
       </c>
       <c r="G22" s="6">
-        <v>1865473491.1199999</v>
+        <v>1882024345.96</v>
       </c>
       <c r="H22" s="6">
-        <v>382822271.44</v>
+        <v>355288273.16000003</v>
       </c>
       <c r="I22" s="6" t="s">
         <v>0</v>
       </c>
       <c r="J22" s="6">
-        <v>237113485.28</v>
+        <v>-350407564.43000001</v>
       </c>
       <c r="K22" s="1">
-        <v>798559369.33000004</v>
+        <v>685868475.12</v>
       </c>
       <c r="L22" s="1">
-        <v>1341883.7</v>
+        <v>7695040.1399999997</v>
       </c>
       <c r="M22" s="1">
-        <v>95026638.439999998</v>
+        <v>15633243.25</v>
       </c>
       <c r="N22" s="1">
-        <v>706592.37</v>
+        <v>104457802.92</v>
       </c>
       <c r="O22" s="1">
-        <v>701484254.82000005</v>
+        <v>558082388.80999994</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>0</v>
@@ -2384,54 +2436,54 @@
         <v>0</v>
       </c>
       <c r="S22" s="1">
-        <v>4374064889.75</v>
+        <v>4052039784.8400002</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B23" s="6">
-        <v>4500844267.8599997</v>
+        <v>4704099845.4399996</v>
       </c>
       <c r="C23" s="6">
-        <v>2476978974.0599999</v>
+        <v>2478033756.71</v>
       </c>
       <c r="D23" s="6">
-        <v>1940517345.4100001</v>
+        <v>1967011743.4000001</v>
       </c>
       <c r="E23" s="6">
-        <v>536461628.64999998</v>
+        <v>511022013.31</v>
       </c>
       <c r="F23" s="6">
-        <v>2268391784.0599999</v>
+        <v>2222932727.5900002</v>
       </c>
       <c r="G23" s="6">
-        <v>1885606076.0999999</v>
+        <v>1868027079.53</v>
       </c>
       <c r="H23" s="6">
-        <v>382785707.95999998</v>
+        <v>354905648.06</v>
       </c>
       <c r="I23" s="6" t="s">
         <v>0</v>
       </c>
       <c r="J23" s="6">
-        <v>-244526490.25999999</v>
+        <v>3133361.14</v>
       </c>
       <c r="K23" s="1">
-        <v>809113264.05999994</v>
+        <v>572925761.97000003</v>
       </c>
       <c r="L23" s="1">
-        <v>1885163.47</v>
+        <v>15098619.939999999</v>
       </c>
       <c r="M23" s="1">
-        <v>76784548.459999993</v>
+        <v>26393500.09</v>
       </c>
       <c r="N23" s="1">
-        <v>2077507.11</v>
+        <v>25306759.550000001</v>
       </c>
       <c r="O23" s="1">
-        <v>728366045.01999998</v>
+        <v>506126882.38999999</v>
       </c>
       <c r="P23" s="6" t="s">
         <v>0</v>
@@ -2443,54 +2495,54 @@
         <v>0</v>
       </c>
       <c r="S23" s="1">
-        <v>3691731003.8000002</v>
+        <v>4131174083.4699998</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B24" s="6">
-        <v>6220002918.9200001</v>
+        <v>5529623295.6599998</v>
       </c>
       <c r="C24" s="6">
-        <v>3277442323.71</v>
+        <v>2785192412.8800001</v>
       </c>
       <c r="D24" s="6">
-        <v>2581010888.3000002</v>
+        <v>2321355687.52</v>
       </c>
       <c r="E24" s="6">
-        <v>696431435.40999997</v>
+        <v>463836725.36000001</v>
       </c>
       <c r="F24" s="6">
-        <v>2744008840.1799998</v>
+        <v>2504665391.9499998</v>
       </c>
       <c r="G24" s="6">
-        <v>2360555370.0100002</v>
+        <v>2148295147.54</v>
       </c>
       <c r="H24" s="6">
-        <v>383453470.17000002</v>
+        <v>356370244.41000003</v>
       </c>
       <c r="I24" s="6" t="s">
         <v>0</v>
       </c>
       <c r="J24" s="6">
-        <v>198551755.03</v>
+        <v>239765490.83000001</v>
       </c>
       <c r="K24" s="1">
-        <v>823728118.88</v>
+        <v>811508446.20000005</v>
       </c>
       <c r="L24" s="1">
-        <v>2035855.77</v>
+        <v>17749943.550000001</v>
       </c>
       <c r="M24" s="1">
-        <v>135138565.62</v>
+        <v>150022534.02000001</v>
       </c>
       <c r="N24" s="1">
-        <v>2768252.56</v>
+        <v>5819731.5700000003</v>
       </c>
       <c r="O24" s="1">
-        <v>683785444.92999995</v>
+        <v>637916237.05999994</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>0</v>
@@ -2502,54 +2554,54 @@
         <v>0</v>
       </c>
       <c r="S24" s="1">
-        <v>5396274800.04</v>
+        <v>4718114849.46</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B25" s="6">
-        <v>8453023582.3500004</v>
+        <v>8243411483.1899996</v>
       </c>
       <c r="C25" s="6">
-        <v>4807690139.7799997</v>
+        <v>4450804743.0699997</v>
       </c>
       <c r="D25" s="6">
-        <v>3578065017.5799999</v>
+        <v>3531477755.5</v>
       </c>
       <c r="E25" s="6">
-        <v>1229625122.2</v>
+        <v>919326987.57000005</v>
       </c>
       <c r="F25" s="6">
-        <v>3845318744.6199999</v>
+        <v>3685098027.6599998</v>
       </c>
       <c r="G25" s="6">
-        <v>3112334663.0900002</v>
+        <v>2994281171.8099999</v>
       </c>
       <c r="H25" s="6">
-        <v>732984081.52999997</v>
+        <v>690816855.85000002</v>
       </c>
       <c r="I25" s="6" t="s">
         <v>0</v>
       </c>
       <c r="J25" s="6">
-        <v>-199985302.05000001</v>
+        <v>107508712.45999999</v>
       </c>
       <c r="K25" s="1">
-        <v>1901471060.5</v>
+        <v>2072486830.4400001</v>
       </c>
       <c r="L25" s="1">
-        <v>1121042.5</v>
+        <v>10722630.08</v>
       </c>
       <c r="M25" s="1">
-        <v>166733719.12</v>
+        <v>453644334.55000001</v>
       </c>
       <c r="N25" s="1">
-        <v>133357198.90000001</v>
+        <v>19216057.120000001</v>
       </c>
       <c r="O25" s="1">
-        <v>1600259099.98</v>
+        <v>1588903808.6900001</v>
       </c>
       <c r="P25" s="6" t="s">
         <v>0</v>
@@ -2561,796 +2613,1468 @@
         <v>0</v>
       </c>
       <c r="S25" s="1">
-        <v>6551552521.8500004</v>
+        <v>6170924652.75</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B26" s="6">
-        <v>5142335256.0799999</v>
+        <v>4360614719.8500004</v>
       </c>
       <c r="C26" s="6">
-        <v>3642206257.1700001</v>
+        <v>2308373595.3499999</v>
       </c>
       <c r="D26" s="6">
-        <v>2741199221.4699998</v>
+        <v>1860038435.97</v>
       </c>
       <c r="E26" s="6">
-        <v>901007035.70000005</v>
+        <v>448335159.38</v>
       </c>
       <c r="F26" s="6">
-        <v>1500128998.9100001</v>
+        <v>2047085583.4400001</v>
       </c>
       <c r="G26" s="6">
-        <v>1126028840.8900001</v>
+        <v>1680765899.24</v>
       </c>
       <c r="H26" s="6">
-        <v>374100158.01999998</v>
+        <v>366319684.19999999</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="J26" s="6" t="s">
-        <v>0</v>
+      <c r="J26" s="6">
+        <v>5155541.0599999996</v>
       </c>
       <c r="K26" s="1">
-        <v>679520374.50999999</v>
+        <v>683044152.41999996</v>
       </c>
       <c r="L26" s="1">
-        <v>1984726.19</v>
+        <v>308745.77</v>
       </c>
       <c r="M26" s="1">
-        <v>5135554.28</v>
+        <v>8093864.46</v>
       </c>
       <c r="N26" s="1">
-        <v>18893959.719999999</v>
+        <v>18501571.800000001</v>
       </c>
       <c r="O26" s="1">
-        <v>651358951.58000004</v>
+        <v>656139970.38999999</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="Q26" s="1">
-        <v>2147182.7400000002</v>
+      <c r="Q26" s="6" t="s">
+        <v>0</v>
       </c>
       <c r="R26" s="6" t="s">
         <v>0</v>
       </c>
       <c r="S26" s="1">
-        <v>4462814881.5699997</v>
+        <v>3677570567.4299998</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B27" s="6">
-        <v>4691575185.7299995</v>
+        <v>4542452747.0600004</v>
       </c>
       <c r="C27" s="6">
-        <v>1788515623.5999999</v>
+        <v>2421454854.4899998</v>
       </c>
       <c r="D27" s="6">
-        <v>1286898239.53</v>
+        <v>1937483038.6300001</v>
       </c>
       <c r="E27" s="6">
-        <v>501617384.06999999</v>
+        <v>483971815.86000001</v>
       </c>
       <c r="F27" s="6">
-        <v>2903059562.1300001</v>
+        <v>2124792912.6099999</v>
       </c>
       <c r="G27" s="6">
-        <v>2503160519.54</v>
+        <v>1768421702.01</v>
       </c>
       <c r="H27" s="6">
-        <v>399899042.58999997</v>
+        <v>356371210.60000002</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="J27" s="6" t="s">
-        <v>0</v>
+      <c r="J27" s="6">
+        <v>-3795020.04</v>
       </c>
       <c r="K27" s="1">
-        <v>1002600580.0700001</v>
+        <v>778229360.70000005</v>
       </c>
       <c r="L27" s="1">
-        <v>2244912.1800000002</v>
+        <v>10543654.33</v>
       </c>
       <c r="M27" s="1">
-        <v>48028278.670000002</v>
+        <v>61631938.899999999</v>
       </c>
       <c r="N27" s="1">
-        <v>9409431.2599999998</v>
+        <v>6392197.6200000001</v>
       </c>
       <c r="O27" s="1">
-        <v>940535228.89999998</v>
+        <v>699661569.85000002</v>
       </c>
       <c r="P27" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="Q27" s="1">
-        <v>2382729.06</v>
+      <c r="Q27" s="6" t="s">
+        <v>0</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>0</v>
       </c>
       <c r="S27" s="1">
-        <v>3688974605.6599998</v>
+        <v>3764223386.3600001</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B28" s="6">
-        <v>4883599518.96</v>
+        <v>4382405735.6599998</v>
       </c>
       <c r="C28" s="6">
-        <v>2683969371.98</v>
+        <v>2281647247.4899998</v>
       </c>
       <c r="D28" s="6">
-        <v>1975101647.3199999</v>
+        <v>1821495612.3900001</v>
       </c>
       <c r="E28" s="6">
-        <v>708867724.65999997</v>
+        <v>460151635.10000002</v>
       </c>
       <c r="F28" s="6">
-        <v>2199607117.0100002</v>
+        <v>2091557285.01</v>
       </c>
       <c r="G28" s="6">
-        <v>1815648950.8</v>
+        <v>1726840987.8599999</v>
       </c>
       <c r="H28" s="6">
-        <v>383958166.20999998</v>
+        <v>364716297.14999998</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>0</v>
       </c>
       <c r="J28" s="6">
-        <v>23029.97</v>
+        <v>9201203.1600000001</v>
       </c>
       <c r="K28" s="1">
-        <v>807372078.05999994</v>
+        <v>751953354.75999999</v>
       </c>
       <c r="L28" s="1">
-        <v>2122054.02</v>
+        <v>8467968.6099999994</v>
       </c>
       <c r="M28" s="1">
-        <v>53015036.189999998</v>
+        <v>16983642.210000001</v>
       </c>
       <c r="N28" s="1">
-        <v>4193813.56</v>
+        <v>6157522.7800000003</v>
       </c>
       <c r="O28" s="1">
-        <v>745467089.14999998</v>
+        <v>720344221.15999997</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="Q28" s="1">
-        <v>2574085.14</v>
+      <c r="Q28" s="6" t="s">
+        <v>0</v>
       </c>
       <c r="R28" s="6" t="s">
         <v>0</v>
       </c>
       <c r="S28" s="1">
-        <v>4076227440.9000001</v>
+        <v>3630452380.9000001</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B29" s="6">
-        <v>4984015573.8199997</v>
+        <v>4408807782.6400003</v>
       </c>
       <c r="C29" s="6">
-        <v>2734803206.9099998</v>
+        <v>2321518043.4299998</v>
       </c>
       <c r="D29" s="6">
-        <v>2020654399.1099999</v>
+        <v>1851831129.55</v>
       </c>
       <c r="E29" s="6">
-        <v>714148807.79999995</v>
+        <v>469686913.88</v>
       </c>
       <c r="F29" s="6">
-        <v>2214173004.7399998</v>
+        <v>2071497606.72</v>
       </c>
       <c r="G29" s="6">
-        <v>1826788057.02</v>
+        <v>1706026430.8800001</v>
       </c>
       <c r="H29" s="6">
-        <v>387384947.72000003</v>
+        <v>365471175.83999997</v>
       </c>
       <c r="I29" s="6" t="s">
         <v>0</v>
       </c>
       <c r="J29" s="6">
-        <v>35039362.170000002</v>
+        <v>15792132.49</v>
       </c>
       <c r="K29" s="1">
-        <v>856657898.13999999</v>
+        <v>690026403.5</v>
       </c>
       <c r="L29" s="1">
-        <v>1553277.45</v>
+        <v>9081298.1500000004</v>
       </c>
       <c r="M29" s="1">
-        <v>31679698.489999998</v>
+        <v>16368983.15</v>
       </c>
       <c r="N29" s="1">
-        <v>3493284.48</v>
+        <v>5605719.7199999997</v>
       </c>
       <c r="O29" s="1">
-        <v>817641788.14999998</v>
+        <v>658970402.48000002</v>
       </c>
       <c r="P29" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="Q29" s="1">
-        <v>2289849.5699999998</v>
+      <c r="Q29" s="6" t="s">
+        <v>0</v>
       </c>
       <c r="R29" s="6" t="s">
         <v>0</v>
       </c>
       <c r="S29" s="1">
-        <v>4127357675.6799998</v>
+        <v>3718781379.1399999</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B30" s="6">
-        <v>5007946385.5699997</v>
+        <v>4421781180.9799995</v>
       </c>
       <c r="C30" s="6">
-        <v>2785761470.8600001</v>
+        <v>2313987463.6599998</v>
       </c>
       <c r="D30" s="6">
-        <v>2012715998.98</v>
+        <v>1842233676.97</v>
       </c>
       <c r="E30" s="6">
-        <v>773045471.88</v>
+        <v>471753786.69</v>
       </c>
       <c r="F30" s="6">
-        <v>2206563488.9899998</v>
+        <v>2093078104.0899999</v>
       </c>
       <c r="G30" s="6">
-        <v>1822646671.9400001</v>
+        <v>1728800627.29</v>
       </c>
       <c r="H30" s="6">
-        <v>383916817.05000001</v>
+        <v>364277476.80000001</v>
       </c>
       <c r="I30" s="6" t="s">
         <v>0</v>
       </c>
       <c r="J30" s="6">
-        <v>15621425.720000001</v>
+        <v>14715613.23</v>
       </c>
       <c r="K30" s="1">
-        <v>878178042.57000005</v>
+        <v>736206792.80999994</v>
       </c>
       <c r="L30" s="1">
-        <v>1368792.06</v>
+        <v>8635039.0199999996</v>
       </c>
       <c r="M30" s="1">
-        <v>24434206.57</v>
+        <v>17474533.399999999</v>
       </c>
       <c r="N30" s="1">
-        <v>9278263.4299999997</v>
+        <v>5729795.8399999999</v>
       </c>
       <c r="O30" s="1">
-        <v>840893745.90999997</v>
+        <v>704367424.54999995</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="Q30" s="1">
-        <v>2203034.6</v>
+      <c r="Q30" s="6" t="s">
+        <v>0</v>
       </c>
       <c r="R30" s="6" t="s">
         <v>0</v>
       </c>
       <c r="S30" s="1">
-        <v>4129768343</v>
+        <v>3685574388.1700001</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B31" s="6">
-        <v>4993844224.0299997</v>
+        <v>4777286303.5699997</v>
       </c>
       <c r="C31" s="6">
-        <v>2699283276.8299999</v>
+        <v>2592886975.6999998</v>
       </c>
       <c r="D31" s="6">
-        <v>1997063186.3599999</v>
+        <v>2117705051.8299999</v>
       </c>
       <c r="E31" s="6">
-        <v>702220090.47000003</v>
+        <v>475181923.87</v>
       </c>
       <c r="F31" s="6">
-        <v>2314318026.0900002</v>
+        <v>2190627210.98</v>
       </c>
       <c r="G31" s="6">
-        <v>1930226795.55</v>
+        <v>1819588794.76</v>
       </c>
       <c r="H31" s="6">
-        <v>384091230.54000002</v>
+        <v>371038416.22000003</v>
       </c>
       <c r="I31" s="6" t="s">
         <v>0</v>
       </c>
       <c r="J31" s="6">
-        <v>-19757078.890000001</v>
+        <v>-6227883.1100000003</v>
       </c>
       <c r="K31" s="1">
-        <v>886877021.58000004</v>
+        <v>899288823.35000002</v>
       </c>
       <c r="L31" s="1">
-        <v>2451823.11</v>
+        <v>1822807.66</v>
       </c>
       <c r="M31" s="1">
-        <v>57125609.030000001</v>
+        <v>203655029.11000001</v>
       </c>
       <c r="N31" s="1">
-        <v>20786745.460000001</v>
+        <v>1571555.6</v>
       </c>
       <c r="O31" s="1">
-        <v>804268379.27999997</v>
+        <v>692239430.98000002</v>
       </c>
       <c r="P31" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="Q31" s="1">
-        <v>2244464.7000000002</v>
+      <c r="Q31" s="6" t="s">
+        <v>0</v>
       </c>
       <c r="R31" s="6" t="s">
         <v>0</v>
       </c>
       <c r="S31" s="1">
-        <v>4106967202.4499998</v>
+        <v>3877997480.2199998</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B32" s="6">
-        <v>5138995524.54</v>
+        <v>4864847110.5699997</v>
       </c>
       <c r="C32" s="6">
-        <v>2870246303.8600001</v>
+        <v>2610035008.9899998</v>
       </c>
       <c r="D32" s="6">
-        <v>2126665619.04</v>
+        <v>2092659098.79</v>
       </c>
       <c r="E32" s="6">
-        <v>743580684.82000005</v>
+        <v>517375910.19999999</v>
       </c>
       <c r="F32" s="6">
-        <v>2289008621.1399999</v>
+        <v>2283192259.6300001</v>
       </c>
       <c r="G32" s="6">
-        <v>1899577514.28</v>
+        <v>1894788001.5799999</v>
       </c>
       <c r="H32" s="6">
-        <v>389431106.86000001</v>
+        <v>388404258.05000001</v>
       </c>
       <c r="I32" s="6" t="s">
         <v>0</v>
       </c>
       <c r="J32" s="6">
-        <v>-20259400.460000001</v>
+        <v>-28380158.050000001</v>
       </c>
       <c r="K32" s="1">
-        <v>873857873.36000001</v>
+        <v>789652575.75</v>
       </c>
       <c r="L32" s="1">
-        <v>2391006.84</v>
+        <v>1708149.44</v>
       </c>
       <c r="M32" s="1">
-        <v>16034527.32</v>
+        <v>45116396.200000003</v>
       </c>
       <c r="N32" s="1">
-        <v>-2585355.5699999998</v>
+        <v>1488125.81</v>
       </c>
       <c r="O32" s="1">
-        <v>855701130.59000003</v>
+        <v>741339904.29999995</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="Q32" s="1">
-        <v>2316564.1800000002</v>
+      <c r="Q32" s="6" t="s">
+        <v>0</v>
       </c>
       <c r="R32" s="6" t="s">
         <v>0</v>
       </c>
       <c r="S32" s="1">
-        <v>4265137651.1799998</v>
+        <v>4075194534.8200002</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B33" s="6">
-        <v>5030147335.2799997</v>
+        <v>4824945641.8100004</v>
       </c>
       <c r="C33" s="6">
-        <v>2687450206.2600002</v>
+        <v>2565043071.4000001</v>
       </c>
       <c r="D33" s="6">
-        <v>2012176785.1900001</v>
+        <v>2056032621.1800001</v>
       </c>
       <c r="E33" s="6">
-        <v>675273421.07000005</v>
+        <v>509010450.22000003</v>
       </c>
       <c r="F33" s="6">
-        <v>2304344660.6399999</v>
+        <v>2257517447.1500001</v>
       </c>
       <c r="G33" s="6">
-        <v>1907276520.5899999</v>
+        <v>1871189395.0599999</v>
       </c>
       <c r="H33" s="6">
-        <v>397068140.05000001</v>
+        <v>386328052.08999997</v>
       </c>
       <c r="I33" s="6" t="s">
         <v>0</v>
       </c>
       <c r="J33" s="6">
-        <v>38352468.380000003</v>
+        <v>2385123.2599999998</v>
       </c>
       <c r="K33" s="1">
-        <v>869406376.99000001</v>
+        <v>778993678.86000001</v>
       </c>
       <c r="L33" s="1">
-        <v>482313.95</v>
+        <v>2161969.98</v>
       </c>
       <c r="M33" s="1">
-        <v>6576529.7000000002</v>
+        <v>99261490.560000002</v>
       </c>
       <c r="N33" s="1">
-        <v>11251206.91</v>
+        <v>3192699.92</v>
       </c>
       <c r="O33" s="1">
-        <v>848693371.51999998</v>
+        <v>674377518.39999998</v>
       </c>
       <c r="P33" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="Q33" s="1">
-        <v>2402954.91</v>
+      <c r="Q33" s="6" t="s">
+        <v>0</v>
       </c>
       <c r="R33" s="6" t="s">
         <v>0</v>
       </c>
       <c r="S33" s="1">
-        <v>4160740958.29</v>
+        <v>4045951962.9499998</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B34" s="6">
-        <v>5145331835.1300001</v>
+        <v>5172624259.0799999</v>
       </c>
       <c r="C34" s="6">
-        <v>2627498329.5600009</v>
+        <v>2687215011.2399998</v>
       </c>
       <c r="D34" s="6">
-        <v>1957924072.95</v>
+        <v>2207789161.1700001</v>
       </c>
       <c r="E34" s="6">
-        <v>669574256.61000097</v>
+        <v>479425850.06999999</v>
       </c>
       <c r="F34" s="6">
-        <v>2314741604.1300001</v>
+        <v>2248295762.5599999</v>
       </c>
       <c r="G34" s="6">
-        <v>1909319063.6500001</v>
+        <v>1865473491.1199999</v>
       </c>
       <c r="H34" s="6">
-        <v>405422540.48000002</v>
+        <v>382822271.44</v>
       </c>
       <c r="I34" s="6" t="s">
         <v>0</v>
       </c>
       <c r="J34" s="6">
-        <v>203091901.44</v>
-      </c>
-      <c r="K34">
-        <v>798410376.64999998</v>
-      </c>
-      <c r="L34">
-        <v>3142882.04</v>
-      </c>
-      <c r="M34">
-        <v>-3088525.3199999901</v>
-      </c>
-      <c r="N34">
-        <v>5119046.55</v>
-      </c>
-      <c r="O34">
-        <v>790834769.98000002</v>
+        <v>237113485.28</v>
+      </c>
+      <c r="K34" s="1">
+        <v>798559369.33000004</v>
+      </c>
+      <c r="L34" s="1">
+        <v>1341883.7</v>
+      </c>
+      <c r="M34" s="1">
+        <v>95026638.439999998</v>
+      </c>
+      <c r="N34" s="1">
+        <v>706592.37</v>
+      </c>
+      <c r="O34" s="1">
+        <v>701484254.82000005</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="Q34">
-        <v>2402203.4</v>
+      <c r="Q34" s="6" t="s">
+        <v>0</v>
       </c>
       <c r="R34" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="S34">
-        <v>4346921458.4800005</v>
+      <c r="S34" s="1">
+        <v>4374064889.75</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B35" s="6">
-        <v>5045992382.8700008</v>
+        <v>4500844267.8599997</v>
       </c>
       <c r="C35" s="6">
-        <v>2938639075.6300011</v>
+        <v>2476978974.0599999</v>
       </c>
       <c r="D35" s="6">
-        <v>2126911147.21</v>
+        <v>1940517345.4100001</v>
       </c>
       <c r="E35" s="6">
-        <v>811727928.42000103</v>
+        <v>536461628.64999998</v>
       </c>
       <c r="F35" s="6">
-        <v>2289402681.1500001</v>
+        <v>2268391784.0599999</v>
       </c>
       <c r="G35" s="6">
-        <v>1892548027.73</v>
+        <v>1885606076.0999999</v>
       </c>
       <c r="H35" s="6">
-        <v>396854653.42000002</v>
+        <v>382785707.95999998</v>
       </c>
       <c r="I35" s="6" t="s">
         <v>0</v>
       </c>
       <c r="J35" s="6">
-        <v>-182049373.91</v>
-      </c>
-      <c r="K35">
-        <v>934717265.91999996</v>
-      </c>
-      <c r="L35">
-        <v>3366325.01</v>
-      </c>
-      <c r="M35">
-        <v>35957642.149999999</v>
-      </c>
-      <c r="N35">
-        <v>4085395.58</v>
-      </c>
-      <c r="O35">
-        <v>888983305.42999995</v>
+        <v>-244526490.25999999</v>
+      </c>
+      <c r="K35" s="1">
+        <v>809113264.05999994</v>
+      </c>
+      <c r="L35" s="1">
+        <v>1885163.47</v>
+      </c>
+      <c r="M35" s="1">
+        <v>76784548.459999993</v>
+      </c>
+      <c r="N35" s="1">
+        <v>2077507.11</v>
+      </c>
+      <c r="O35" s="1">
+        <v>728366045.01999998</v>
       </c>
       <c r="P35" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="Q35">
-        <v>2324597.75</v>
+      <c r="Q35" s="6" t="s">
+        <v>0</v>
       </c>
       <c r="R35" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="S35">
-        <v>4111275116.9500008</v>
+      <c r="S35" s="1">
+        <v>3691731003.8000002</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B36" s="6">
-        <v>6426921051.710001</v>
+        <v>6220002918.9200001</v>
       </c>
       <c r="C36" s="6">
-        <v>3522622551.0999999</v>
+        <v>3277442323.71</v>
       </c>
       <c r="D36" s="6">
-        <v>2594771895.3499999</v>
+        <v>2581010888.3000002</v>
       </c>
       <c r="E36" s="6">
-        <v>927850655.75</v>
+        <v>696431435.40999997</v>
       </c>
       <c r="F36" s="6">
-        <v>2956851497.0900002</v>
+        <v>2744008840.1799998</v>
       </c>
       <c r="G36" s="6">
-        <v>2568993743.73</v>
+        <v>2360555370.0100002</v>
       </c>
       <c r="H36" s="6">
-        <v>387857753.36000001</v>
+        <v>383453470.17000002</v>
       </c>
       <c r="I36" s="6" t="s">
         <v>0</v>
       </c>
       <c r="J36" s="6">
-        <v>-52552996.479999997</v>
-      </c>
-      <c r="K36">
-        <v>960336017.18000019</v>
-      </c>
-      <c r="L36">
-        <v>3785554.62</v>
-      </c>
-      <c r="M36">
-        <v>140925785.08000001</v>
-      </c>
-      <c r="N36">
-        <v>14646485.470000001</v>
-      </c>
-      <c r="O36">
-        <v>798717481.44000006</v>
+        <v>198551755.03</v>
+      </c>
+      <c r="K36" s="1">
+        <v>823728118.88</v>
+      </c>
+      <c r="L36" s="1">
+        <v>2035855.77</v>
+      </c>
+      <c r="M36" s="1">
+        <v>135138565.62</v>
+      </c>
+      <c r="N36" s="1">
+        <v>2768252.56</v>
+      </c>
+      <c r="O36" s="1">
+        <v>683785444.92999995</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="Q36">
-        <v>2260710.5699999998</v>
+      <c r="Q36" s="6" t="s">
+        <v>0</v>
       </c>
       <c r="R36" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="S36">
-        <v>5466585034.5300007</v>
+      <c r="S36" s="1">
+        <v>5396274800.04</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B37" s="6">
-        <v>9000020094.9299984</v>
+        <v>8453023582.3500004</v>
       </c>
       <c r="C37" s="6">
-        <v>5225739140.5</v>
+        <v>4807690139.7799997</v>
       </c>
       <c r="D37" s="6">
-        <v>3795852684.7600002</v>
+        <v>3578065017.5799999</v>
       </c>
       <c r="E37" s="6">
-        <v>1429886455.74</v>
+        <v>1229625122.2</v>
       </c>
       <c r="F37" s="6">
-        <v>3791790292.3699999</v>
+        <v>3845318744.6199999</v>
       </c>
       <c r="G37" s="6">
-        <v>3034713783.1799998</v>
+        <v>3112334663.0900002</v>
       </c>
       <c r="H37" s="6">
-        <v>757076509.19000006</v>
+        <v>732984081.52999997</v>
       </c>
       <c r="I37" s="6" t="s">
         <v>0</v>
       </c>
       <c r="J37" s="6">
-        <v>-17509337.940000001</v>
-      </c>
-      <c r="K37">
-        <v>2075450542.8800001</v>
-      </c>
-      <c r="L37">
-        <v>1140691.83</v>
-      </c>
-      <c r="M37">
-        <v>302213228.23000002</v>
-      </c>
-      <c r="N37">
-        <v>14854856.460000001</v>
-      </c>
-      <c r="O37">
-        <v>1755018355.47</v>
+        <v>-199985302.05000001</v>
+      </c>
+      <c r="K37" s="1">
+        <v>1901471060.5</v>
+      </c>
+      <c r="L37" s="1">
+        <v>1121042.5</v>
+      </c>
+      <c r="M37" s="1">
+        <v>166733719.12</v>
+      </c>
+      <c r="N37" s="1">
+        <v>133357198.90000001</v>
+      </c>
+      <c r="O37" s="1">
+        <v>1600259099.98</v>
       </c>
       <c r="P37" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="Q37">
-        <v>2223410.89</v>
+      <c r="Q37" s="6" t="s">
+        <v>0</v>
       </c>
       <c r="R37" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="S37">
+      <c r="S37" s="1">
+        <v>6551552521.8500004</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38" s="6">
+        <v>5142335256.0799999</v>
+      </c>
+      <c r="C38" s="6">
+        <v>3642206257.1700001</v>
+      </c>
+      <c r="D38" s="6">
+        <v>2741199221.4699998</v>
+      </c>
+      <c r="E38" s="6">
+        <v>901007035.70000005</v>
+      </c>
+      <c r="F38" s="6">
+        <v>1500128998.9100001</v>
+      </c>
+      <c r="G38" s="6">
+        <v>1126028840.8900001</v>
+      </c>
+      <c r="H38" s="6">
+        <v>374100158.01999998</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="K38" s="1">
+        <v>679520374.50999999</v>
+      </c>
+      <c r="L38" s="1">
+        <v>1984726.19</v>
+      </c>
+      <c r="M38" s="1">
+        <v>5135554.28</v>
+      </c>
+      <c r="N38" s="1">
+        <v>18893959.719999999</v>
+      </c>
+      <c r="O38" s="1">
+        <v>651358951.58000004</v>
+      </c>
+      <c r="P38" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>2147182.7400000002</v>
+      </c>
+      <c r="R38" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="S38" s="1">
+        <v>4462814881.5699997</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" s="6">
+        <v>4691575185.7299995</v>
+      </c>
+      <c r="C39" s="6">
+        <v>1788515623.5999999</v>
+      </c>
+      <c r="D39" s="6">
+        <v>1286898239.53</v>
+      </c>
+      <c r="E39" s="6">
+        <v>501617384.06999999</v>
+      </c>
+      <c r="F39" s="6">
+        <v>2903059562.1300001</v>
+      </c>
+      <c r="G39" s="6">
+        <v>2503160519.54</v>
+      </c>
+      <c r="H39" s="6">
+        <v>399899042.58999997</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="K39" s="1">
+        <v>1002600580.0700001</v>
+      </c>
+      <c r="L39" s="1">
+        <v>2244912.1800000002</v>
+      </c>
+      <c r="M39" s="1">
+        <v>48028278.670000002</v>
+      </c>
+      <c r="N39" s="1">
+        <v>9409431.2599999998</v>
+      </c>
+      <c r="O39" s="1">
+        <v>940535228.89999998</v>
+      </c>
+      <c r="P39" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="1">
+        <v>2382729.06</v>
+      </c>
+      <c r="R39" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="S39" s="1">
+        <v>3688974605.6599998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B40" s="6">
+        <v>4883599518.96</v>
+      </c>
+      <c r="C40" s="6">
+        <v>2683969371.98</v>
+      </c>
+      <c r="D40" s="6">
+        <v>1975101647.3199999</v>
+      </c>
+      <c r="E40" s="6">
+        <v>708867724.65999997</v>
+      </c>
+      <c r="F40" s="6">
+        <v>2199607117.0100002</v>
+      </c>
+      <c r="G40" s="6">
+        <v>1815648950.8</v>
+      </c>
+      <c r="H40" s="6">
+        <v>383958166.20999998</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="J40" s="6">
+        <v>23029.97</v>
+      </c>
+      <c r="K40" s="1">
+        <v>807372078.05999994</v>
+      </c>
+      <c r="L40" s="1">
+        <v>2122054.02</v>
+      </c>
+      <c r="M40" s="1">
+        <v>53015036.189999998</v>
+      </c>
+      <c r="N40" s="1">
+        <v>4193813.56</v>
+      </c>
+      <c r="O40" s="1">
+        <v>745467089.14999998</v>
+      </c>
+      <c r="P40" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>2574085.14</v>
+      </c>
+      <c r="R40" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="S40" s="1">
+        <v>4076227440.9000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B41" s="6">
+        <v>4984015573.8199997</v>
+      </c>
+      <c r="C41" s="6">
+        <v>2734803206.9099998</v>
+      </c>
+      <c r="D41" s="6">
+        <v>2020654399.1099999</v>
+      </c>
+      <c r="E41" s="6">
+        <v>714148807.79999995</v>
+      </c>
+      <c r="F41" s="6">
+        <v>2214173004.7399998</v>
+      </c>
+      <c r="G41" s="6">
+        <v>1826788057.02</v>
+      </c>
+      <c r="H41" s="6">
+        <v>387384947.72000003</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="J41" s="6">
+        <v>35039362.170000002</v>
+      </c>
+      <c r="K41" s="1">
+        <v>856657898.13999999</v>
+      </c>
+      <c r="L41" s="1">
+        <v>1553277.45</v>
+      </c>
+      <c r="M41" s="1">
+        <v>31679698.489999998</v>
+      </c>
+      <c r="N41" s="1">
+        <v>3493284.48</v>
+      </c>
+      <c r="O41" s="1">
+        <v>817641788.14999998</v>
+      </c>
+      <c r="P41" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>2289849.5699999998</v>
+      </c>
+      <c r="R41" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="S41" s="1">
+        <v>4127357675.6799998</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="6">
+        <v>5007946385.5699997</v>
+      </c>
+      <c r="C42" s="6">
+        <v>2785761470.8600001</v>
+      </c>
+      <c r="D42" s="6">
+        <v>2012715998.98</v>
+      </c>
+      <c r="E42" s="6">
+        <v>773045471.88</v>
+      </c>
+      <c r="F42" s="6">
+        <v>2206563488.9899998</v>
+      </c>
+      <c r="G42" s="6">
+        <v>1822646671.9400001</v>
+      </c>
+      <c r="H42" s="6">
+        <v>383916817.05000001</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="J42" s="6">
+        <v>15621425.720000001</v>
+      </c>
+      <c r="K42" s="1">
+        <v>878178042.57000005</v>
+      </c>
+      <c r="L42" s="1">
+        <v>1368792.06</v>
+      </c>
+      <c r="M42" s="1">
+        <v>24434206.57</v>
+      </c>
+      <c r="N42" s="1">
+        <v>9278263.4299999997</v>
+      </c>
+      <c r="O42" s="1">
+        <v>840893745.90999997</v>
+      </c>
+      <c r="P42" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="1">
+        <v>2203034.6</v>
+      </c>
+      <c r="R42" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="S42" s="1">
+        <v>4129768343</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B43" s="6">
+        <v>4993844224.0299997</v>
+      </c>
+      <c r="C43" s="6">
+        <v>2699283276.8299999</v>
+      </c>
+      <c r="D43" s="6">
+        <v>1997063186.3599999</v>
+      </c>
+      <c r="E43" s="6">
+        <v>702220090.47000003</v>
+      </c>
+      <c r="F43" s="6">
+        <v>2314318026.0900002</v>
+      </c>
+      <c r="G43" s="6">
+        <v>1930226795.55</v>
+      </c>
+      <c r="H43" s="6">
+        <v>384091230.54000002</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="J43" s="6">
+        <v>-19757078.890000001</v>
+      </c>
+      <c r="K43" s="1">
+        <v>886877021.58000004</v>
+      </c>
+      <c r="L43" s="1">
+        <v>2451823.11</v>
+      </c>
+      <c r="M43" s="1">
+        <v>57125609.030000001</v>
+      </c>
+      <c r="N43" s="1">
+        <v>20786745.460000001</v>
+      </c>
+      <c r="O43" s="1">
+        <v>804268379.27999997</v>
+      </c>
+      <c r="P43" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="1">
+        <v>2244464.7000000002</v>
+      </c>
+      <c r="R43" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="S43" s="1">
+        <v>4106967202.4499998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" s="6">
+        <v>5138995524.54</v>
+      </c>
+      <c r="C44" s="6">
+        <v>2870246303.8600001</v>
+      </c>
+      <c r="D44" s="6">
+        <v>2126665619.04</v>
+      </c>
+      <c r="E44" s="6">
+        <v>743580684.82000005</v>
+      </c>
+      <c r="F44" s="6">
+        <v>2289008621.1399999</v>
+      </c>
+      <c r="G44" s="6">
+        <v>1899577514.28</v>
+      </c>
+      <c r="H44" s="6">
+        <v>389431106.86000001</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="J44" s="6">
+        <v>-20259400.460000001</v>
+      </c>
+      <c r="K44" s="1">
+        <v>873857873.36000001</v>
+      </c>
+      <c r="L44" s="1">
+        <v>2391006.84</v>
+      </c>
+      <c r="M44" s="1">
+        <v>16034527.32</v>
+      </c>
+      <c r="N44" s="1">
+        <v>-2585355.5699999998</v>
+      </c>
+      <c r="O44" s="1">
+        <v>855701130.59000003</v>
+      </c>
+      <c r="P44" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>2316564.1800000002</v>
+      </c>
+      <c r="R44" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="S44" s="1">
+        <v>4265137651.1799998</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B45" s="6">
+        <v>5030147335.2799997</v>
+      </c>
+      <c r="C45" s="6">
+        <v>2687450206.2600002</v>
+      </c>
+      <c r="D45" s="6">
+        <v>2012176785.1900001</v>
+      </c>
+      <c r="E45" s="6">
+        <v>675273421.07000005</v>
+      </c>
+      <c r="F45" s="6">
+        <v>2304344660.6399999</v>
+      </c>
+      <c r="G45" s="6">
+        <v>1907276520.5899999</v>
+      </c>
+      <c r="H45" s="6">
+        <v>397068140.05000001</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="J45" s="6">
+        <v>38352468.380000003</v>
+      </c>
+      <c r="K45" s="1">
+        <v>869406376.99000001</v>
+      </c>
+      <c r="L45" s="1">
+        <v>482313.95</v>
+      </c>
+      <c r="M45" s="1">
+        <v>6576529.7000000002</v>
+      </c>
+      <c r="N45" s="1">
+        <v>11251206.91</v>
+      </c>
+      <c r="O45" s="1">
+        <v>848693371.51999998</v>
+      </c>
+      <c r="P45" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="1">
+        <v>2402954.91</v>
+      </c>
+      <c r="R45" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="S45" s="1">
+        <v>4160740958.29</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B46" s="6">
+        <v>5145331835.1300001</v>
+      </c>
+      <c r="C46" s="6">
+        <v>2627498329.5600009</v>
+      </c>
+      <c r="D46" s="6">
+        <v>1957924072.95</v>
+      </c>
+      <c r="E46" s="6">
+        <v>669574256.61000097</v>
+      </c>
+      <c r="F46" s="6">
+        <v>2314741604.1300001</v>
+      </c>
+      <c r="G46" s="6">
+        <v>1909319063.6500001</v>
+      </c>
+      <c r="H46" s="6">
+        <v>405422540.48000002</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="J46" s="6">
+        <v>203091901.44</v>
+      </c>
+      <c r="K46">
+        <v>798410376.64999998</v>
+      </c>
+      <c r="L46">
+        <v>3142882.04</v>
+      </c>
+      <c r="M46">
+        <v>-3088525.3199999901</v>
+      </c>
+      <c r="N46">
+        <v>5119046.55</v>
+      </c>
+      <c r="O46">
+        <v>790834769.98000002</v>
+      </c>
+      <c r="P46" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>2402203.4</v>
+      </c>
+      <c r="R46" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>4346921458.4800005</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B47" s="6">
+        <v>5045992382.8700008</v>
+      </c>
+      <c r="C47" s="6">
+        <v>2938639075.6300011</v>
+      </c>
+      <c r="D47" s="6">
+        <v>2126911147.21</v>
+      </c>
+      <c r="E47" s="6">
+        <v>811727928.42000103</v>
+      </c>
+      <c r="F47" s="6">
+        <v>2289402681.1500001</v>
+      </c>
+      <c r="G47" s="6">
+        <v>1892548027.73</v>
+      </c>
+      <c r="H47" s="6">
+        <v>396854653.42000002</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="J47" s="6">
+        <v>-182049373.91</v>
+      </c>
+      <c r="K47">
+        <v>934717265.91999996</v>
+      </c>
+      <c r="L47">
+        <v>3366325.01</v>
+      </c>
+      <c r="M47">
+        <v>35957642.149999999</v>
+      </c>
+      <c r="N47">
+        <v>4085395.58</v>
+      </c>
+      <c r="O47">
+        <v>888983305.42999995</v>
+      </c>
+      <c r="P47" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>2324597.75</v>
+      </c>
+      <c r="R47" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>4111275116.9500008</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B48" s="6">
+        <v>6426921051.710001</v>
+      </c>
+      <c r="C48" s="6">
+        <v>3522622551.0999999</v>
+      </c>
+      <c r="D48" s="6">
+        <v>2594771895.3499999</v>
+      </c>
+      <c r="E48" s="6">
+        <v>927850655.75</v>
+      </c>
+      <c r="F48" s="6">
+        <v>2956851497.0900002</v>
+      </c>
+      <c r="G48" s="6">
+        <v>2568993743.73</v>
+      </c>
+      <c r="H48" s="6">
+        <v>387857753.36000001</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="J48" s="6">
+        <v>-52552996.479999997</v>
+      </c>
+      <c r="K48">
+        <v>960336017.18000019</v>
+      </c>
+      <c r="L48">
+        <v>3785554.62</v>
+      </c>
+      <c r="M48">
+        <v>140925785.08000001</v>
+      </c>
+      <c r="N48">
+        <v>14646485.470000001</v>
+      </c>
+      <c r="O48">
+        <v>798717481.44000006</v>
+      </c>
+      <c r="P48" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>2260710.5699999998</v>
+      </c>
+      <c r="R48" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>5466585034.5300007</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B49" s="6">
+        <v>9000020094.9299984</v>
+      </c>
+      <c r="C49" s="6">
+        <v>5225739140.5</v>
+      </c>
+      <c r="D49" s="6">
+        <v>3795852684.7600002</v>
+      </c>
+      <c r="E49" s="6">
+        <v>1429886455.74</v>
+      </c>
+      <c r="F49" s="6">
+        <v>3791790292.3699999</v>
+      </c>
+      <c r="G49" s="6">
+        <v>3034713783.1799998</v>
+      </c>
+      <c r="H49" s="6">
+        <v>757076509.19000006</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="J49" s="6">
+        <v>-17509337.940000001</v>
+      </c>
+      <c r="K49">
+        <v>2075450542.8800001</v>
+      </c>
+      <c r="L49">
+        <v>1140691.83</v>
+      </c>
+      <c r="M49">
+        <v>302213228.23000002</v>
+      </c>
+      <c r="N49">
+        <v>14854856.460000001</v>
+      </c>
+      <c r="O49">
+        <v>1755018355.47</v>
+      </c>
+      <c r="P49" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>2223410.89</v>
+      </c>
+      <c r="R49" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="S49">
         <v>6924569552.0499983</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A38" s="4"/>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A39" s="4"/>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A40" s="4"/>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A41" s="4"/>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A42" s="4"/>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A43" s="4"/>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A44" s="4"/>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A45" s="4"/>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A46" s="4"/>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A47" s="4"/>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A48" s="4"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="4"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" s="4"/>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" s="4"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="4"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" s="4"/>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" s="4"/>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" s="4"/>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" s="4"/>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" s="4"/>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" s="4"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" s="4"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" s="4"/>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
@@ -52324,6 +53048,42 @@
     </row>
     <row r="16388" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16388" s="4"/>
+    </row>
+    <row r="16389" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16389" s="4"/>
+    </row>
+    <row r="16390" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16390" s="4"/>
+    </row>
+    <row r="16391" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16391" s="4"/>
+    </row>
+    <row r="16392" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16392" s="4"/>
+    </row>
+    <row r="16393" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16393" s="4"/>
+    </row>
+    <row r="16394" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16394" s="4"/>
+    </row>
+    <row r="16395" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16395" s="4"/>
+    </row>
+    <row r="16396" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16396" s="4"/>
+    </row>
+    <row r="16397" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16397" s="4"/>
+    </row>
+    <row r="16398" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16398" s="4"/>
+    </row>
+    <row r="16399" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16399" s="4"/>
+    </row>
+    <row r="16400" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16400" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
